--- a/exports/600519.SH_20260315.xlsx
+++ b/exports/600519.SH_20260315.xlsx
@@ -436,7 +436,7 @@
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
@@ -564,24 +564,32 @@
         <v>21.64</v>
       </c>
       <c r="I2" t="n">
-        <v>33607.83</v>
+        <v>33608</v>
       </c>
       <c r="J2" t="n">
         <v>4738808.558</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>1400.904</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1407.304</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1448.6865</v>
+      </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-9.538324811890561</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>-1.584868464148798</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+        <v>-7.953456347741763</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>30.13197294000233</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -613,24 +621,32 @@
         <v>-8</v>
       </c>
       <c r="I3" t="n">
-        <v>27586.46</v>
+        <v>27586</v>
       </c>
       <c r="J3" t="n">
         <v>3850521.717</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>1398.576</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1411.442</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1455.7545</v>
+      </c>
       <c r="N3" t="n">
-        <v>-1.72626780626797</v>
+        <v>-9.931877404827446</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.345253561253594</v>
+        <v>0.403495622786643</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.381014245014376</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+        <v>-10.33537302761409</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>20.43750000000011</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -662,24 +678,32 @@
         <v>-1.88</v>
       </c>
       <c r="I4" t="n">
-        <v>24456.73</v>
+        <v>24457</v>
       </c>
       <c r="J4" t="n">
         <v>3425363.892</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>1399.984</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1418.863</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1462.4045</v>
+      </c>
       <c r="N4" t="n">
-        <v>-2.420907622503137</v>
+        <v>-8.086384497560175</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7603843735035025</v>
+        <v>2.987338879690165</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.660523248999634</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>-11.07372337725034</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>19.26589288870569</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -711,24 +735,32 @@
         <v>4.88</v>
       </c>
       <c r="I5" t="n">
-        <v>24625.92</v>
+        <v>24626</v>
       </c>
       <c r="J5" t="n">
         <v>3457808.916</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>1400.22</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1428.029</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1466.1505</v>
+      </c>
       <c r="N5" t="n">
-        <v>-2.787580895935434</v>
+        <v>-6.427789775956398</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.165823677989889</v>
+        <v>5.75576972400275</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.621757217945546</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>-12.18355949995915</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>19.42728136882141</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -760,26 +792,32 @@
         <v>-5</v>
       </c>
       <c r="I6" t="n">
-        <v>37441.62</v>
+        <v>37442</v>
       </c>
       <c r="J6" t="n">
         <v>5220095.639</v>
       </c>
       <c r="K6" t="n">
-        <v>1400.904</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+        <v>1405.082</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1434.521</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1467.4065</v>
+      </c>
       <c r="N6" t="n">
-        <v>-3.432380971747534</v>
+        <v>-4.408742843640994</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.619135136741418</v>
+        <v>8.801659598992536</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.813245835006116</v>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+        <v>-13.21040244263353</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>15.15250544662315</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -811,26 +849,32 @@
         <v>2.96</v>
       </c>
       <c r="I7" t="n">
-        <v>29154.15</v>
+        <v>29154</v>
       </c>
       <c r="J7" t="n">
         <v>4072328.833</v>
       </c>
       <c r="K7" t="n">
-        <v>1398.576</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+        <v>1413.704</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1443.351</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1467.6065</v>
+      </c>
       <c r="N7" t="n">
-        <v>-3.499590364799815</v>
+        <v>-1.270704863214632</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.995226182353098</v>
+        <v>12.10426020965092</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.504364182446717</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+        <v>-13.37496507286555</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>20.03182179793164</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -862,26 +906,32 @@
         <v>-2.14</v>
       </c>
       <c r="I8" t="n">
-        <v>30505.24</v>
+        <v>30505</v>
       </c>
       <c r="J8" t="n">
         <v>4276226.062</v>
       </c>
       <c r="K8" t="n">
-        <v>1399.984</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+        <v>1424.308</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1451.811</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1469.3925</v>
+      </c>
       <c r="N8" t="n">
-        <v>-3.748491281125325</v>
+        <v>2.243964775267159</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.345879202107543</v>
+        <v>15.4480014778673</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.402612079017782</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+        <v>-13.20403670260014</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>15.43133256494374</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -913,26 +963,32 @@
         <v>-25.01</v>
       </c>
       <c r="I9" t="n">
-        <v>48014.43</v>
+        <v>48014</v>
       </c>
       <c r="J9" t="n">
         <v>6743267.103</v>
       </c>
       <c r="K9" t="n">
-        <v>1400.22</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+        <v>1437.742</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1462.34</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1465.625</v>
+      </c>
       <c r="N9" t="n">
-        <v>-3.73006902148154</v>
+        <v>6.998703626198221</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.622717165982343</v>
+        <v>18.74901065351734</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.107351855499198</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+        <v>-11.75030702731912</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>25.57212752525257</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -964,26 +1020,32 @@
         <v>-13.92</v>
       </c>
       <c r="I10" t="n">
-        <v>45890.86</v>
+        <v>45891</v>
       </c>
       <c r="J10" t="n">
         <v>6565381.648</v>
       </c>
       <c r="K10" t="n">
-        <v>1405.082</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+        <v>1455.838</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1472.702</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1462.7165</v>
+      </c>
       <c r="N10" t="n">
-        <v>-1.678028002997053</v>
+        <v>12.74778916136916</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.433779333385285</v>
+        <v>21.68658741034712</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7557513303882324</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+        <v>-8.93879824897796</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>41.25166062259883</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1015,28 +1077,32 @@
         <v>-14.91</v>
       </c>
       <c r="I11" t="n">
-        <v>35453.86</v>
+        <v>35454</v>
       </c>
       <c r="J11" t="n">
         <v>5115063.511</v>
       </c>
       <c r="K11" t="n">
-        <v>1413.704</v>
+        <v>1463.96</v>
       </c>
       <c r="L11" t="n">
-        <v>1407.304</v>
-      </c>
-      <c r="M11" t="inlineStr"/>
+        <v>1482.579</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1458.507</v>
+      </c>
       <c r="N11" t="n">
-        <v>1.059246618356838</v>
+        <v>17.35381776573126</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.735174143036861</v>
+        <v>23.9212869725916</v>
       </c>
       <c r="P11" t="n">
-        <v>2.794420761393698</v>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+        <v>-6.567469206860338</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>52.09753287894786</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1068,28 +1134,32 @@
         <v>-11.19</v>
       </c>
       <c r="I12" t="n">
-        <v>32160.16</v>
+        <v>32160</v>
       </c>
       <c r="J12" t="n">
         <v>4697692.477</v>
       </c>
       <c r="K12" t="n">
-        <v>1424.308</v>
+        <v>1472.998</v>
       </c>
       <c r="L12" t="n">
-        <v>1411.442</v>
-      </c>
-      <c r="M12" t="inlineStr"/>
+        <v>1490.069</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1453.3515</v>
+      </c>
       <c r="N12" t="n">
-        <v>4.381165519778278</v>
+        <v>21.56305692597903</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5119062104738329</v>
+        <v>25.56315427430669</v>
       </c>
       <c r="P12" t="n">
-        <v>4.893071730252111</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+        <v>-4.00009734832766</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>58.34672435105067</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1121,28 +1191,32 @@
         <v>-25.45</v>
       </c>
       <c r="I13" t="n">
-        <v>32958.01</v>
+        <v>32958</v>
       </c>
       <c r="J13" t="n">
         <v>4855471.43</v>
       </c>
       <c r="K13" t="n">
-        <v>1437.742</v>
+        <v>1479.314</v>
       </c>
       <c r="L13" t="n">
-        <v>1418.863</v>
-      </c>
-      <c r="M13" t="inlineStr"/>
+        <v>1500.067</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1447.6035</v>
+      </c>
       <c r="N13" t="n">
-        <v>7.826530294170652</v>
+        <v>25.10382317159042</v>
       </c>
       <c r="O13" t="n">
-        <v>1.155781090455064</v>
+        <v>26.5631786113886</v>
       </c>
       <c r="P13" t="n">
-        <v>6.670749203715588</v>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+        <v>-1.45935543979818</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>54.08014206742475</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1174,28 +1248,32 @@
         <v>24.86</v>
       </c>
       <c r="I14" t="n">
-        <v>36880.67</v>
+        <v>36881</v>
       </c>
       <c r="J14" t="n">
         <v>5490316.149</v>
       </c>
       <c r="K14" t="n">
-        <v>1455.838</v>
+        <v>1486.938</v>
       </c>
       <c r="L14" t="n">
-        <v>1428.029</v>
-      </c>
-      <c r="M14" t="inlineStr"/>
+        <v>1505.946</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1441.846</v>
+      </c>
       <c r="N14" t="n">
-        <v>12.46689836192354</v>
+        <v>28.11863647894756</v>
       </c>
       <c r="O14" t="n">
-        <v>3.41800454474876</v>
+        <v>26.92801747133814</v>
       </c>
       <c r="P14" t="n">
-        <v>9.048893817174781</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+        <v>1.190619007609421</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>69.18736149505379</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1227,29 +1305,31 @@
         <v>-18.5</v>
       </c>
       <c r="I15" t="n">
-        <v>41912.53</v>
+        <v>41913</v>
       </c>
       <c r="J15" t="n">
         <v>6198840.572</v>
       </c>
       <c r="K15" t="n">
-        <v>1463.96</v>
+        <v>1489.566</v>
       </c>
       <c r="L15" t="n">
-        <v>1434.521</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
+        <v>1504.272</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1435.9405</v>
+      </c>
       <c r="N15" t="n">
-        <v>13.97730755048292</v>
+        <v>28.96636347882577</v>
       </c>
       <c r="O15" t="n">
-        <v>5.529865145895592</v>
+        <v>26.63036271943579</v>
       </c>
       <c r="P15" t="n">
-        <v>8.447442404587328</v>
+        <v>2.336000759389982</v>
       </c>
       <c r="Q15" t="n">
-        <v>66.42362827483925</v>
+        <v>64.32191035934932</v>
       </c>
     </row>
     <row r="16">
@@ -1282,29 +1362,31 @@
         <v>-1.3</v>
       </c>
       <c r="I16" t="n">
-        <v>41679.01</v>
+        <v>41679</v>
       </c>
       <c r="J16" t="n">
         <v>6216379.203</v>
       </c>
       <c r="K16" t="n">
-        <v>1472.998</v>
+        <v>1501.198</v>
       </c>
       <c r="L16" t="n">
-        <v>1443.351</v>
-      </c>
-      <c r="M16" t="inlineStr"/>
+        <v>1500.292</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1431.4005</v>
+      </c>
       <c r="N16" t="n">
-        <v>16.47717449251104</v>
+        <v>32.15824247170576</v>
       </c>
       <c r="O16" t="n">
-        <v>7.719327015218681</v>
+        <v>26.04636252958829</v>
       </c>
       <c r="P16" t="n">
-        <v>8.757847477292358</v>
+        <v>6.111879942117472</v>
       </c>
       <c r="Q16" t="n">
-        <v>69.86802705999767</v>
+        <v>67.27838333172566</v>
       </c>
     </row>
     <row r="17">
@@ -1337,29 +1419,31 @@
         <v>-17.73</v>
       </c>
       <c r="I17" t="n">
-        <v>46245.82</v>
+        <v>46246</v>
       </c>
       <c r="J17" t="n">
         <v>6874370.113</v>
       </c>
       <c r="K17" t="n">
-        <v>1479.314</v>
+        <v>1507.14</v>
       </c>
       <c r="L17" t="n">
-        <v>1451.811</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
+        <v>1491.862</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1426.2355</v>
+      </c>
       <c r="N17" t="n">
-        <v>18.35168933891464</v>
+        <v>33.88084813212049</v>
       </c>
       <c r="O17" t="n">
-        <v>9.845799479957874</v>
+        <v>24.51839254405892</v>
       </c>
       <c r="P17" t="n">
-        <v>8.505889858956765</v>
+        <v>9.362455588061572</v>
       </c>
       <c r="Q17" t="n">
-        <v>79.56249999999989</v>
+        <v>67.87848367512785</v>
       </c>
     </row>
     <row r="18">
@@ -1392,29 +1476,31 @@
         <v>-0.47</v>
       </c>
       <c r="I18" t="n">
-        <v>30928.46</v>
+        <v>30928</v>
       </c>
       <c r="J18" t="n">
         <v>4648360.03</v>
       </c>
       <c r="K18" t="n">
-        <v>1486.938</v>
+        <v>1520.82</v>
       </c>
       <c r="L18" t="n">
-        <v>1462.34</v>
-      </c>
-      <c r="M18" t="inlineStr"/>
+        <v>1486.974</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1421.35</v>
+      </c>
       <c r="N18" t="n">
-        <v>21.02554924035439</v>
+        <v>35.45434338403697</v>
       </c>
       <c r="O18" t="n">
-        <v>12.08174943203718</v>
+        <v>22.17777864704352</v>
       </c>
       <c r="P18" t="n">
-        <v>8.943799808317216</v>
+        <v>13.27656473699345</v>
       </c>
       <c r="Q18" t="n">
-        <v>80.73410711129431</v>
+        <v>70.34504966436303</v>
       </c>
     </row>
     <row r="19">
@@ -1447,29 +1533,31 @@
         <v>-20.16</v>
       </c>
       <c r="I19" t="n">
-        <v>39575.96</v>
+        <v>39576</v>
       </c>
       <c r="J19" t="n">
         <v>5953269.321</v>
       </c>
       <c r="K19" t="n">
-        <v>1489.566</v>
+        <v>1524.954</v>
       </c>
       <c r="L19" t="n">
-        <v>1472.702</v>
-      </c>
-      <c r="M19" t="inlineStr"/>
+        <v>1468.91</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1416.034</v>
+      </c>
       <c r="N19" t="n">
-        <v>22.91833920028171</v>
+        <v>35.14175960180637</v>
       </c>
       <c r="O19" t="n">
-        <v>14.24906738568608</v>
+        <v>18.85863746279516</v>
       </c>
       <c r="P19" t="n">
-        <v>8.669271814595623</v>
+        <v>16.28312213901121</v>
       </c>
       <c r="Q19" t="n">
-        <v>80.57271863117859</v>
+        <v>68.55687524140595</v>
       </c>
     </row>
     <row r="20">
@@ -1502,29 +1590,29 @@
         <v>9.949999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>51168.46</v>
+        <v>51168</v>
       </c>
       <c r="J20" t="n">
         <v>7809067.705</v>
       </c>
       <c r="K20" t="n">
-        <v>1501.198</v>
+        <v>1518.978</v>
       </c>
       <c r="L20" t="n">
-        <v>1482.579</v>
+        <v>1452.731</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
-        <v>25.74832177059193</v>
+        <v>34.18378161646024</v>
       </c>
       <c r="O20" t="n">
-        <v>16.54891826266725</v>
+        <v>14.78785692804235</v>
       </c>
       <c r="P20" t="n">
-        <v>9.199403507924675</v>
+        <v>19.39592468841789</v>
       </c>
       <c r="Q20" t="n">
-        <v>84.84749455337685</v>
+        <v>68.17341623256597</v>
       </c>
     </row>
     <row r="21">
@@ -1557,31 +1645,29 @@
         <v>-39.99</v>
       </c>
       <c r="I21" t="n">
-        <v>78965.38</v>
+        <v>78965</v>
       </c>
       <c r="J21" t="n">
         <v>12019878.669</v>
       </c>
       <c r="K21" t="n">
-        <v>1507.14</v>
+        <v>1499.386</v>
       </c>
       <c r="L21" t="n">
-        <v>1490.069</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1448.6865</v>
-      </c>
+        <v>1434.435</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
-        <v>26.87838422003051</v>
+        <v>30.41118016437895</v>
       </c>
       <c r="O21" t="n">
-        <v>18.61481145413991</v>
+        <v>9.938875755937882</v>
       </c>
       <c r="P21" t="n">
-        <v>8.263572765890604</v>
+        <v>20.47230440844107</v>
       </c>
       <c r="Q21" t="n">
-        <v>79.96817820206834</v>
+        <v>66.99097953895421</v>
       </c>
     </row>
     <row r="22">
@@ -1614,31 +1700,29 @@
         <v>30</v>
       </c>
       <c r="I22" t="n">
-        <v>91622.74000000001</v>
+        <v>91623</v>
       </c>
       <c r="J22" t="n">
         <v>14183456.476</v>
       </c>
       <c r="K22" t="n">
-        <v>1520.82</v>
+        <v>1476.584</v>
       </c>
       <c r="L22" t="n">
-        <v>1500.067</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1455.7545</v>
-      </c>
+        <v>1416.634</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
-        <v>30.64753988018856</v>
+        <v>26.16671532678583</v>
       </c>
       <c r="O22" t="n">
-        <v>21.02135713934964</v>
+        <v>4.820799653827615</v>
       </c>
       <c r="P22" t="n">
-        <v>9.626182740838921</v>
+        <v>21.34591567295822</v>
       </c>
       <c r="Q22" t="n">
-        <v>84.56866743505626</v>
+        <v>73.0617468273435</v>
       </c>
     </row>
     <row r="23">
@@ -1671,31 +1755,29 @@
         <v>50.08</v>
       </c>
       <c r="I23" t="n">
-        <v>109122.93</v>
+        <v>109123</v>
       </c>
       <c r="J23" t="n">
         <v>16444345.98</v>
       </c>
       <c r="K23" t="n">
-        <v>1524.954</v>
+        <v>1453.128</v>
       </c>
       <c r="L23" t="n">
-        <v>1505.946</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1462.4045</v>
-      </c>
+        <v>1395.14</v>
+      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>30.85815995717644</v>
+        <v>16.29691889295918</v>
       </c>
       <c r="O23" t="n">
-        <v>22.988717702915</v>
+        <v>-0.5156792644119399</v>
       </c>
       <c r="P23" t="n">
-        <v>7.86944225426144</v>
+        <v>16.81259815737112</v>
       </c>
       <c r="Q23" t="n">
-        <v>74.42787247474743</v>
+        <v>69.33545472625507</v>
       </c>
     </row>
     <row r="24">
@@ -1728,31 +1810,29 @@
         <v>47.92</v>
       </c>
       <c r="I24" t="n">
-        <v>86320.66</v>
+        <v>86321</v>
       </c>
       <c r="J24" t="n">
         <v>12628439.703</v>
       </c>
       <c r="K24" t="n">
-        <v>1518.978</v>
+        <v>1412.866</v>
       </c>
       <c r="L24" t="n">
-        <v>1504.272</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1466.1505</v>
-      </c>
+        <v>1377.746</v>
+      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>26.67652998949256</v>
+        <v>6.516968988068584</v>
       </c>
       <c r="O24" t="n">
-        <v>23.72628016023052</v>
+        <v>-4.718828803754721</v>
       </c>
       <c r="P24" t="n">
-        <v>2.950249829262049</v>
+        <v>11.23579779182331</v>
       </c>
       <c r="Q24" t="n">
-        <v>58.74833937740117</v>
+        <v>62.36455419439891</v>
       </c>
     </row>
     <row r="25">
@@ -1785,31 +1865,29 @@
         <v>26</v>
       </c>
       <c r="I25" t="n">
-        <v>85724.27</v>
+        <v>85724</v>
       </c>
       <c r="J25" t="n">
         <v>12312646.443</v>
       </c>
       <c r="K25" t="n">
-        <v>1499.386</v>
+        <v>1386.484</v>
       </c>
       <c r="L25" t="n">
-        <v>1500.292</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1467.4065</v>
-      </c>
+        <v>1367.609</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>19.27364007191136</v>
+        <v>-0.9615411667275566</v>
       </c>
       <c r="O25" t="n">
-        <v>22.83575214256669</v>
+        <v>-7.527778251710547</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.562112070655328</v>
+        <v>6.566237084982991</v>
       </c>
       <c r="Q25" t="n">
-        <v>47.90246712105215</v>
+        <v>55.50952145653579</v>
       </c>
     </row>
     <row r="26">
@@ -1842,32 +1920,28 @@
         <v>-36.72</v>
       </c>
       <c r="I26" t="n">
-        <v>94479.74000000001</v>
+        <v>94480</v>
       </c>
       <c r="J26" t="n">
         <v>13366329.414</v>
       </c>
       <c r="K26" t="n">
-        <v>1476.584</v>
+        <v>1369.484</v>
       </c>
       <c r="L26" t="n">
-        <v>1491.862</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1467.6065</v>
-      </c>
+        <v>1362.509</v>
+      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>11.17993839777296</v>
+        <v>-5.613726256423661</v>
       </c>
       <c r="O26" t="n">
-        <v>20.50458939360794</v>
+        <v>-9.169337522956294</v>
       </c>
       <c r="P26" t="n">
-        <v>-9.324650995834983</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>41.65327564894933</v>
-      </c>
+        <v>3.555611266532633</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1899,32 +1973,28 @@
         <v>114.03</v>
       </c>
       <c r="I27" t="n">
-        <v>189534.4</v>
+        <v>189534</v>
       </c>
       <c r="J27" t="n">
         <v>26305591.086</v>
       </c>
       <c r="K27" t="n">
-        <v>1453.128</v>
+        <v>1356.684</v>
       </c>
       <c r="L27" t="n">
-        <v>1486.974</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1469.3925</v>
-      </c>
+        <v>1360.609</v>
+      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>7.640543201251148</v>
+        <v>-8.82267920717868</v>
       </c>
       <c r="O27" t="n">
-        <v>17.93178015513658</v>
+        <v>-10.05824033958945</v>
       </c>
       <c r="P27" t="n">
-        <v>-10.29123695388543</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>45.91985793257525</v>
-      </c>
+        <v>1.235561132410771</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1956,32 +2026,28 @@
         <v>-19.32</v>
       </c>
       <c r="I28" t="n">
-        <v>76218.00999999999</v>
+        <v>76218</v>
       </c>
       <c r="J28" t="n">
         <v>10135019.524</v>
       </c>
       <c r="K28" t="n">
-        <v>1412.866</v>
+        <v>1337.152</v>
       </c>
       <c r="L28" t="n">
-        <v>1468.91</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1465.625</v>
-      </c>
+        <v>1355.726</v>
+      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>-4.315969197177537</v>
+        <v>-16.52890382131068</v>
       </c>
       <c r="O28" t="n">
-        <v>13.48223028467376</v>
+        <v>-10.36713062269214</v>
       </c>
       <c r="P28" t="n">
-        <v>-17.7981994818513</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>30.81263850494621</v>
-      </c>
+        <v>-6.161773198618535</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2013,32 +2079,28 @@
         <v>1.01</v>
       </c>
       <c r="I29" t="n">
-        <v>48415.96</v>
+        <v>48416</v>
       </c>
       <c r="J29" t="n">
         <v>6514513.216</v>
       </c>
       <c r="K29" t="n">
-        <v>1386.484</v>
+        <v>1342.626</v>
       </c>
       <c r="L29" t="n">
-        <v>1452.731</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1462.7165</v>
-      </c>
+        <v>1363.158</v>
+      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>-12.0932257008219</v>
+        <v>-14.51410100049293</v>
       </c>
       <c r="O29" t="n">
-        <v>8.367139087574627</v>
+        <v>-8.826687323037508</v>
       </c>
       <c r="P29" t="n">
-        <v>-20.46036478839653</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>35.67808964065067</v>
-      </c>
+        <v>-5.687413677455421</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2070,32 +2132,26 @@
         <v>5</v>
       </c>
       <c r="I30" t="n">
-        <v>80166.06</v>
+        <v>80166</v>
       </c>
       <c r="J30" t="n">
         <v>10751225.525</v>
       </c>
       <c r="K30" t="n">
-        <v>1369.484</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1434.435</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1458.507</v>
-      </c>
+        <v>1348.734</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>-18.12927309597535</v>
+        <v>-13.69849302191506</v>
       </c>
       <c r="O30" t="n">
-        <v>3.067856650864631</v>
+        <v>-7.404833903673652</v>
       </c>
       <c r="P30" t="n">
-        <v>-21.19712974683998</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>32.72161666827434</v>
-      </c>
+        <v>-6.293659118241403</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2127,32 +2183,26 @@
         <v>-3.06</v>
       </c>
       <c r="I31" t="n">
-        <v>61948.9</v>
+        <v>61949</v>
       </c>
       <c r="J31" t="n">
         <v>8301311.489</v>
       </c>
       <c r="K31" t="n">
-        <v>1356.684</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1416.634</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1453.3515</v>
-      </c>
+        <v>1355.534</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>-23.05062905404748</v>
+        <v>-12.35539348530233</v>
       </c>
       <c r="O31" t="n">
-        <v>-2.15584049011779</v>
+        <v>-5.8314191241133</v>
       </c>
       <c r="P31" t="n">
-        <v>-20.89478856392969</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>32.12151632487215</v>
-      </c>
+        <v>-6.523974361189029</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2184,32 +2234,26 @@
         <v>-11</v>
       </c>
       <c r="I32" t="n">
-        <v>59010.89</v>
+        <v>59011</v>
       </c>
       <c r="J32" t="n">
         <v>7962441.434</v>
       </c>
       <c r="K32" t="n">
-        <v>1337.152</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1395.14</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1447.6035</v>
-      </c>
+        <v>1364.534</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>-26.39960447357362</v>
+        <v>-9.952304353330192</v>
       </c>
       <c r="O32" t="n">
-        <v>-7.004593286808956</v>
+        <v>-4.200425533816042</v>
       </c>
       <c r="P32" t="n">
-        <v>-19.39501118676466</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>29.65495033563697</v>
-      </c>
+        <v>-5.751878819514149</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2241,32 +2285,26 @@
         <v>-22.49</v>
       </c>
       <c r="I33" t="n">
-        <v>64516.25</v>
+        <v>64516</v>
       </c>
       <c r="J33" t="n">
         <v>8775880.802999999</v>
       </c>
       <c r="K33" t="n">
-        <v>1342.626</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1377.746</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1441.846</v>
-      </c>
+        <v>1374.3</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>-27.84510254330394</v>
+        <v>-7.051891616110197</v>
       </c>
       <c r="O33" t="n">
-        <v>-11.17269513810795</v>
+        <v>-2.762455828937505</v>
       </c>
       <c r="P33" t="n">
-        <v>-16.67240740519598</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>31.44312475859405</v>
-      </c>
+        <v>-4.289435787172692</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2298,32 +2336,26 @@
         <v>-2.45</v>
       </c>
       <c r="I34" t="n">
-        <v>36484.43</v>
+        <v>36484</v>
       </c>
       <c r="J34" t="n">
         <v>5021900.765</v>
       </c>
       <c r="K34" t="n">
-        <v>1348.734</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1367.609</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1435.9405</v>
-      </c>
+        <v>1383.69</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>-26.86621809601797</v>
+        <v>-4.36733729891489</v>
       </c>
       <c r="O34" t="n">
-        <v>-14.31139972968996</v>
+        <v>-1.690096882144331</v>
       </c>
       <c r="P34" t="n">
-        <v>-12.55481836632802</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>31.82658376743403</v>
-      </c>
+        <v>-2.677240416770559</v>
+      </c>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2355,32 +2387,24 @@
         <v>-6</v>
       </c>
       <c r="I35" t="n">
-        <v>42286.4</v>
+        <v>42286</v>
       </c>
       <c r="J35" t="n">
         <v>5833745.442</v>
       </c>
-      <c r="K35" t="n">
-        <v>1355.534</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1362.509</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1431.4005</v>
-      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
-        <v>-25.59767651371681</v>
+        <v>-3.16723579152881</v>
       </c>
       <c r="O35" t="n">
-        <v>-16.56865508649533</v>
+        <v>-1.020786777951691</v>
       </c>
       <c r="P35" t="n">
-        <v>-9.029021427221476</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>33.00902046104579</v>
-      </c>
+        <v>-2.146449013577119</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2412,32 +2436,24 @@
         <v>-6.89</v>
       </c>
       <c r="I36" t="n">
-        <v>55120.68</v>
+        <v>55121</v>
       </c>
       <c r="J36" t="n">
         <v>7643061.998</v>
       </c>
-      <c r="K36" t="n">
-        <v>1364.534</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1360.609</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1426.2355</v>
-      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
-        <v>-23.83346101175766</v>
+        <v>-1.838855528769955</v>
       </c>
       <c r="O36" t="n">
-        <v>-18.0216162715478</v>
+        <v>-0.4841745245574112</v>
       </c>
       <c r="P36" t="n">
-        <v>-5.811844740209867</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>26.93825317265649</v>
-      </c>
+        <v>-1.354681004212543</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2469,32 +2485,24 @@
         <v>-9.119999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>40907.14</v>
+        <v>40907</v>
       </c>
       <c r="J37" t="n">
         <v>5698739.671</v>
       </c>
-      <c r="K37" t="n">
-        <v>1374.3</v>
-      </c>
-      <c r="L37" t="n">
-        <v>1355.726</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1421.35</v>
-      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
-        <v>-21.63000486621422</v>
+        <v>-0.7275213675213763</v>
       </c>
       <c r="O37" t="n">
-        <v>-18.74329399048108</v>
+        <v>-0.1455042735042753</v>
       </c>
       <c r="P37" t="n">
-        <v>-2.88671087573314</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>30.66454527374493</v>
-      </c>
+        <v>-0.582017094017101</v>
+      </c>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2526,32 +2534,24 @@
         <v>-12.99</v>
       </c>
       <c r="I38" t="n">
-        <v>51757.97</v>
+        <v>51758</v>
       </c>
       <c r="J38" t="n">
         <v>7285041.159</v>
       </c>
-      <c r="K38" t="n">
-        <v>1383.69</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1363.158</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1416.034</v>
-      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
-        <v>-18.92963318675743</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>-18.78056182973635</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>-0.1490713570210751</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>37.63544580560109</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
